--- a/ksoft/docs/fields_details/Supplier_Fields_Detail.xlsx
+++ b/ksoft/docs/fields_details/Supplier_Fields_Detail.xlsx
@@ -1272,13 +1272,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CCB1FCC-F582-429E-A8A4-FB8491138C91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25B9F954-3EF8-4906-97CD-A847F2E0A619}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B8F9393-1988-4A00-85E7-3669DA4B6294}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE901B80-C273-4D94-ABB8-EC32654C45C3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BC162F5-ACFD-48B3-9E1D-9CBF24F0AC8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85741EEA-0BB4-4E27-B46D-7BB7EFE7F9F8}"/>
 </file>
--- a/ksoft/docs/fields_details/Supplier_Fields_Detail.xlsx
+++ b/ksoft/docs/fields_details/Supplier_Fields_Detail.xlsx
@@ -1272,13 +1272,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25B9F954-3EF8-4906-97CD-A847F2E0A619}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CCB1FCC-F582-429E-A8A4-FB8491138C91}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE901B80-C273-4D94-ABB8-EC32654C45C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B8F9393-1988-4A00-85E7-3669DA4B6294}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85741EEA-0BB4-4E27-B46D-7BB7EFE7F9F8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BC162F5-ACFD-48B3-9E1D-9CBF24F0AC8C}"/>
 </file>